--- a/Project4596_D. Cusco(2025).xlsx
+++ b/Project4596_D. Cusco(2025).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\domin\Downloads\Desktop\Year 3\diss\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\neotrans\inst\matrices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46D45321-88C4-47F0-B28D-AA5CED67DA1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA5BBE21-E085-4F63-8F18-A98F3432DAB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{9BDC09A0-1C88-40E6-9E7D-BB4F554851C3}"/>
   </bookViews>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="46">
   <si>
     <t>Charlabels</t>
   </si>
@@ -768,6 +768,9 @@
       <c r="B10" t="s">
         <v>41</v>
       </c>
+      <c r="D10" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
@@ -818,6 +821,9 @@
       <c r="B14" t="s">
         <v>42</v>
       </c>
+      <c r="D14" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
@@ -871,6 +877,9 @@
       <c r="C18" t="s">
         <v>40</v>
       </c>
+      <c r="D18" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
@@ -893,6 +902,9 @@
       <c r="B20" t="s">
         <v>43</v>
       </c>
+      <c r="D20" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
@@ -901,6 +913,9 @@
       <c r="B21" t="s">
         <v>43</v>
       </c>
+      <c r="D21" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
@@ -936,6 +951,9 @@
       </c>
       <c r="B24" s="3" t="s">
         <v>43</v>
+      </c>
+      <c r="D24" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
